--- a/output/roomself_excel/9098.xlsx
+++ b/output/roomself_excel/9098.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>125543</v>
+        <v>108101</v>
       </c>
       <c r="D2" t="n">
-        <v>2976</v>
+        <v>2812</v>
       </c>
       <c r="E2" t="n">
-        <v>470</v>
+        <v>254</v>
       </c>
       <c r="F2" t="n">
-        <v>346</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>107690</v>
+        <v>108144</v>
       </c>
       <c r="D3" t="n">
-        <v>2748</v>
+        <v>2804</v>
       </c>
       <c r="E3" t="n">
-        <v>377</v>
+        <v>228</v>
       </c>
       <c r="F3" t="n">
-        <v>284</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>108135</v>
+        <v>125543</v>
       </c>
       <c r="D4" t="n">
-        <v>2752</v>
+        <v>2976</v>
       </c>
       <c r="E4" t="n">
-        <v>243</v>
+        <v>470</v>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>125079</v>
+        <v>107690</v>
       </c>
       <c r="D5" t="n">
-        <v>2972</v>
+        <v>2748</v>
       </c>
       <c r="E5" t="n">
-        <v>470</v>
+        <v>377</v>
       </c>
       <c r="F5" t="n">
-        <v>345</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>421253</v>
+        <v>108135</v>
       </c>
       <c r="D6" t="n">
-        <v>7828</v>
+        <v>2752</v>
       </c>
       <c r="E6" t="n">
-        <v>1175</v>
+        <v>243</v>
       </c>
       <c r="F6" t="n">
-        <v>599</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>420716</v>
+        <v>125079</v>
       </c>
       <c r="D7" t="n">
-        <v>7823</v>
+        <v>2972</v>
       </c>
       <c r="E7" t="n">
-        <v>1073</v>
+        <v>470</v>
       </c>
       <c r="F7" t="n">
-        <v>599</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>59409</v>
+        <v>40458</v>
       </c>
       <c r="D8" t="n">
-        <v>1976</v>
+        <v>1832</v>
       </c>
       <c r="E8" t="n">
-        <v>287</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>59202</v>
+        <v>40608</v>
       </c>
       <c r="D9" t="n">
-        <v>1972</v>
+        <v>1836</v>
       </c>
       <c r="E9" t="n">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21413</v>
+        <v>14842</v>
       </c>
       <c r="D10" t="n">
-        <v>1176</v>
+        <v>1052</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21384</v>
+        <v>14299</v>
       </c>
       <c r="D11" t="n">
-        <v>1176</v>
+        <v>1040</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>40458</v>
+        <v>36288</v>
       </c>
       <c r="D12" t="n">
-        <v>1832</v>
+        <v>1524</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>40608</v>
+        <v>36702</v>
       </c>
       <c r="D13" t="n">
-        <v>1836</v>
+        <v>1572</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14">
@@ -730,17 +730,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14842</v>
+        <v>59409</v>
       </c>
       <c r="D14" t="n">
-        <v>1052</v>
+        <v>1976</v>
       </c>
       <c r="E14" t="n">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="F14" t="n">
         <v>36</v>
@@ -752,20 +752,152 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14299</v>
+        <v>59202</v>
       </c>
       <c r="D15" t="n">
-        <v>1040</v>
+        <v>1972</v>
       </c>
       <c r="E15" t="n">
-        <v>79</v>
+        <v>286</v>
       </c>
       <c r="F15" t="n">
         <v>36</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>42347</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2304</v>
+      </c>
+      <c r="E16" t="n">
+        <v>419</v>
+      </c>
+      <c r="F16" t="n">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>41653</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2291</v>
+      </c>
+      <c r="E17" t="n">
+        <v>314</v>
+      </c>
+      <c r="F17" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>21413</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1176</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>21384</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1176</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>234474</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3964</v>
+      </c>
+      <c r="E20" t="n">
+        <v>599</v>
+      </c>
+      <c r="F20" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>234260</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3964</v>
+      </c>
+      <c r="E21" t="n">
+        <v>599</v>
+      </c>
+      <c r="F21" t="n">
+        <v>464</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/9098.xlsx
+++ b/output/roomself_excel/9098.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,12 @@
       <c r="D2" t="n">
         <v>2812</v>
       </c>
-      <c r="E2" t="n">
-        <v>254</v>
-      </c>
-      <c r="F2" t="n">
-        <v>93</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +517,12 @@
       <c r="D3" t="n">
         <v>2804</v>
       </c>
-      <c r="E3" t="n">
-        <v>228</v>
-      </c>
-      <c r="F3" t="n">
-        <v>213</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +539,27 @@
       <c r="D4" t="n">
         <v>2976</v>
       </c>
-      <c r="E4" t="n">
-        <v>470</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>346</v>
+        <v>310</v>
+      </c>
+      <c r="G4" t="n">
+        <v>36</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>434</v>
+      </c>
+      <c r="J4" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +577,20 @@
       <c r="D5" t="n">
         <v>2748</v>
       </c>
-      <c r="E5" t="n">
-        <v>377</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>284</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="G5" t="n">
+        <v>36</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +607,20 @@
       <c r="D6" t="n">
         <v>2752</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>243</v>
       </c>
-      <c r="F6" t="n">
-        <v>36</v>
-      </c>
+      <c r="G6" t="n">
+        <v>36</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +637,27 @@
       <c r="D7" t="n">
         <v>2972</v>
       </c>
-      <c r="E7" t="n">
-        <v>470</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>345</v>
+        <v>309</v>
+      </c>
+      <c r="G7" t="n">
+        <v>36</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>434</v>
+      </c>
+      <c r="J7" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -607,12 +675,12 @@
       <c r="D8" t="n">
         <v>1832</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +697,12 @@
       <c r="D9" t="n">
         <v>1836</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +719,20 @@
       <c r="D10" t="n">
         <v>1052</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>82</v>
       </c>
-      <c r="F10" t="n">
-        <v>36</v>
-      </c>
+      <c r="G10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +749,20 @@
       <c r="D11" t="n">
         <v>1040</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>79</v>
       </c>
-      <c r="F11" t="n">
-        <v>36</v>
-      </c>
+      <c r="G11" t="n">
+        <v>36</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +779,20 @@
       <c r="D12" t="n">
         <v>1524</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>192</v>
       </c>
-      <c r="F12" t="n">
-        <v>36</v>
-      </c>
+      <c r="G12" t="n">
+        <v>36</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +809,20 @@
       <c r="D13" t="n">
         <v>1572</v>
       </c>
-      <c r="E13" t="n">
-        <v>224</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>202</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="G13" t="n">
+        <v>36</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +839,20 @@
       <c r="D14" t="n">
         <v>1976</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>287</v>
       </c>
-      <c r="F14" t="n">
-        <v>36</v>
-      </c>
+      <c r="G14" t="n">
+        <v>36</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +869,20 @@
       <c r="D15" t="n">
         <v>1972</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>286</v>
       </c>
-      <c r="F15" t="n">
-        <v>36</v>
-      </c>
+      <c r="G15" t="n">
+        <v>36</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +899,12 @@
       <c r="D16" t="n">
         <v>2304</v>
       </c>
-      <c r="E16" t="n">
-        <v>419</v>
-      </c>
-      <c r="F16" t="n">
-        <v>344</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +921,12 @@
       <c r="D17" t="n">
         <v>2291</v>
       </c>
-      <c r="E17" t="n">
-        <v>314</v>
-      </c>
-      <c r="F17" t="n">
-        <v>254</v>
-      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +943,12 @@
       <c r="D18" t="n">
         <v>1176</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +965,12 @@
       <c r="D19" t="n">
         <v>1176</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,11 +987,27 @@
       <c r="D20" t="n">
         <v>3964</v>
       </c>
-      <c r="E20" t="n">
-        <v>599</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>464</v>
+        <v>427</v>
+      </c>
+      <c r="G20" t="n">
+        <v>36</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>563</v>
+      </c>
+      <c r="J20" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="21">
@@ -893,11 +1025,27 @@
       <c r="D21" t="n">
         <v>3964</v>
       </c>
-      <c r="E21" t="n">
-        <v>599</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F21" t="n">
-        <v>464</v>
+        <v>427</v>
+      </c>
+      <c r="G21" t="n">
+        <v>36</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>563</v>
+      </c>
+      <c r="J21" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/9098.xlsx
+++ b/output/roomself_excel/9098.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,46 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
         </is>
       </c>
     </row>
@@ -501,6 +541,14 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -523,6 +571,14 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -561,6 +617,26 @@
       <c r="J4" t="n">
         <v>36</v>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>153</v>
+      </c>
+      <c r="N4" t="n">
+        <v>36</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -591,6 +667,26 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>154</v>
+      </c>
+      <c r="N5" t="n">
+        <v>36</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -621,6 +717,26 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>153</v>
+      </c>
+      <c r="N6" t="n">
+        <v>36</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -659,6 +775,26 @@
       <c r="J7" t="n">
         <v>36</v>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>155</v>
+      </c>
+      <c r="N7" t="n">
+        <v>36</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -681,6 +817,14 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -703,6 +847,14 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -733,6 +885,14 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -763,6 +923,14 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -793,6 +961,26 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>120</v>
+      </c>
+      <c r="N12" t="n">
+        <v>36</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -823,6 +1011,26 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>116</v>
+      </c>
+      <c r="N13" t="n">
+        <v>36</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -853,6 +1061,26 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>88</v>
+      </c>
+      <c r="N14" t="n">
+        <v>36</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -883,6 +1111,26 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>90</v>
+      </c>
+      <c r="N15" t="n">
+        <v>36</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -905,6 +1153,14 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -927,6 +1183,14 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -949,6 +1213,14 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -971,6 +1243,14 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1009,6 +1289,38 @@
       <c r="J20" t="n">
         <v>36</v>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>348</v>
+      </c>
+      <c r="N20" t="n">
+        <v>36</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>89</v>
+      </c>
+      <c r="R20" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1045,6 +1357,38 @@
         <v>563</v>
       </c>
       <c r="J21" t="n">
+        <v>36</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>348</v>
+      </c>
+      <c r="N21" t="n">
+        <v>36</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>90</v>
+      </c>
+      <c r="R21" t="n">
         <v>36</v>
       </c>
     </row>
